--- a/data/trans_bre/IP04D$colectiva-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Estudios-trans_bre.xlsx
@@ -632,17 +632,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 1,89</t>
+          <t>-4,75; 1,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,59</t>
+          <t>0,0; 7,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 7,55</t>
+          <t>-0,78; 7,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,19</t>
+          <t>-1,19; 2,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,37</t>
+          <t>-0,69; 2,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,59</t>
+          <t>-2,45; 2,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 143,37</t>
+          <t>-40,32; 172,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,98; 299,2</t>
+          <t>-32,98; 253,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 62,11</t>
+          <t>-36,81; 57,13</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 6,24</t>
+          <t>-1,98; 6,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 1,84</t>
+          <t>-7,73; 2,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 10,27</t>
+          <t>-3,32; 10,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-35,35; 222,42</t>
+          <t>-35,22; 272,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,09; 30,64</t>
+          <t>-59,55; 30,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 92,27</t>
+          <t>-21,64; 95,69</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,29</t>
+          <t>-0,69; 2,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,54</t>
+          <t>-1,76; 1,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,37</t>
+          <t>-1,6; 3,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,49; 113,18</t>
+          <t>-20,46; 123,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,14; 53,53</t>
+          <t>-40,08; 53,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 56,13</t>
+          <t>-20,56; 53,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$colectiva-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Estudios-trans_bre.xlsx
@@ -632,17 +632,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 1,89</t>
+          <t>-5,03; 1,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,32</t>
+          <t>0,0; 6,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 7,47</t>
+          <t>-0,69; 7,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,34</t>
+          <t>-1,25; 2,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,24</t>
+          <t>-0,55; 2,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,38</t>
+          <t>-2,33; 2,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,32; 172,67</t>
+          <t>-42,17; 162,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,98; 253,64</t>
+          <t>-29,42; 243,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 57,13</t>
+          <t>-37,13; 62,81</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 6,56</t>
+          <t>-2,09; 6,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 2,18</t>
+          <t>-7,8; 2,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 10,69</t>
+          <t>-2,91; 10,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-35,22; 272,1</t>
+          <t>-36,48; 232,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,55; 30,47</t>
+          <t>-61,01; 35,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 95,69</t>
+          <t>-17,0; 100,58</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,4</t>
+          <t>-0,73; 2,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,55</t>
+          <t>-1,76; 1,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,24</t>
+          <t>-1,32; 3,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 123,67</t>
+          <t>-23,29; 99,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,08; 53,79</t>
+          <t>-38,89; 53,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 53,34</t>
+          <t>-17,05; 55,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$colectiva-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Estudios-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción colectiva en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>2,43</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>253,92%</t>
+          <t>386,02%</t>
         </is>
       </c>
     </row>
@@ -632,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,79</t>
+          <t>-4,84; 1,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,34</t>
+          <t>0,0; 5,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 7,97</t>
+          <t>-0,63; 9,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,32</t>
+          <t>-1,02; 2,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,26</t>
+          <t>-0,63; 2,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,55</t>
+          <t>-1,8; 3,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,17; 162,89</t>
+          <t>-35,5; 143,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,42; 243,96</t>
+          <t>-34,98; 299,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,13; 62,81</t>
+          <t>-28,93; 73,42</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>4,45</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>33,79%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 6,15</t>
+          <t>-1,77; 6,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 2,36</t>
+          <t>-7,9; 1,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 10,77</t>
+          <t>-2,64; 10,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-36,48; 232,56</t>
+          <t>-35,35; 222,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,01; 35,43</t>
+          <t>-62,09; 30,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 100,58</t>
+          <t>-16,68; 100,56</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,24</t>
+          <t>-0,98; 2,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,44</t>
+          <t>-1,65; 1,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,36</t>
+          <t>-0,76; 4,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 99,67</t>
+          <t>-28,49; 113,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,89; 53,49</t>
+          <t>-39,14; 53,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 55,27</t>
+          <t>-10,69; 72,65</t>
         </is>
       </c>
     </row>
